--- a/reports/evidence_report.xlsx
+++ b/reports/evidence_report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,17 +29,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="0000D4FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00C8D8E8"/>
       <sz val="9"/>
     </font>
     <font>
@@ -51,7 +46,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="000D6EFD"/>
       <sz val="14"/>
     </font>
     <font>
@@ -73,22 +68,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="000D1B2A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="000A1520"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,23 +102,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="002A3A4A"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="002A3A4A"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="002A3A4A"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="002A3A4A"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,17 +129,20 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,8 +527,11 @@
     <col width="36" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -616,10 +617,25 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Risk Score</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Timestomping</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Evidence Collected On</t>
         </is>
@@ -671,7 +687,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 12:14:09</t>
+          <t>2026-04-07 12:13:54</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -681,7 +697,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -701,17 +717,26 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Billing &amp; Financial</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10 15:03:55</t>
+      <c r="S2" s="2" t="n">
+        <v>4.6898</v>
+      </c>
+      <c r="T2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -733,12 +758,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>billing_payment_summary.txt</t>
+          <t>ehr_case_summary_P001.txt</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>healthcare_data\billing\billing_payment_summary.txt</t>
+          <t>healthcare_data\EHR\ehr_case_summary_P001.txt</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -747,7 +772,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -761,7 +786,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-07 12:14:12</t>
+          <t>2026-04-07 12:13:54</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -771,17 +796,17 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>a928668c6b8a5442daba9e16ea964dfb1e347d6dbff7e63b9ffc0e12f98e7d55</t>
+          <t>fc6e6ceaee54d233eb0a122cb1ceee2fa7009fa48b9b12088737036f7bd41eee</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>395e12e67a76d8f106d3ffbe7f3f7b15</t>
+          <t>30dbc5c86afde117badb70bf2cfbc1bf</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -789,19 +814,28 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Billing &amp; Financial</t>
-        </is>
+      <c r="Q3" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:55</t>
+          <t>Electronic Health Record</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>5.0459</v>
+      </c>
+      <c r="T3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -823,12 +857,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ehr_case_summary_P001.txt</t>
+          <t>billing_payment_summary.txt</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>healthcare_data\EHR\ehr_case_summary_P001.txt</t>
+          <t>healthcare_data\billing\billing_payment_summary.txt</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -837,7 +871,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -851,47 +885,56 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 12:14:15</t>
+          <t>2026-04-13 11:23:30</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 12:13:54</t>
+          <t>2026-04-13 11:23:30</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>fc6e6ceaee54d233eb0a122cb1ceee2fa7009fa48b9b12088737036f7bd41eee</t>
+          <t>25dd2ddb7f4435a684f563ad12eb56ea7730d9d289572388b800b8fd52ccde1f</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30dbc5c86afde117badb70bf2cfbc1bf</t>
+          <t>1f922ad1dadf8930eca130c5a0c43cd6</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Electronic Health Record</t>
-        </is>
+          <t>Modified After Breach</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:55</t>
+          <t>Billing &amp; Financial</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>4.6736</v>
+      </c>
+      <c r="T4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -913,12 +956,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ehr_patient_records.csv</t>
+          <t>lab_test_results_2026.csv</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>healthcare_data\EHR\ehr_patient_records.csv</t>
+          <t>healthcare_data\lab reports\lab_test_results_2026.csv</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -927,7 +970,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.29</v>
+        <v>2.91</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -941,7 +984,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-07 12:14:18</t>
+          <t>2026-04-07 12:13:54</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -951,17 +994,17 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>8aead1e5ff7f49a39aaac45d7ab3075ac1c5aec63998d654e88c3b95c95efb74</t>
+          <t>ef9f2d5b367cbf71c1ddaf1ebd7af7973271ed0fda77eb0a56b149df755f0aaa</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>3af5ca6cb0272db6e103b237a5dc1fe6</t>
+          <t>cd35e3d18d28c56919fabdb451d23a0a</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -971,17 +1014,26 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Electronic Health Record</t>
-        </is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:55</t>
+          <t>Laboratory Report</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>5.1902</v>
+      </c>
+      <c r="T5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1055,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>lab_report_P003_cardiac.txt</t>
+          <t>pharmacy_drug_inventory.txt</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>healthcare_data\lab reports\lab_report_P003_cardiac.txt</t>
+          <t>healthcare_data\Pharmacy\pharmacy_drug_inventory.txt</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1017,7 +1069,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -1031,47 +1083,56 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 12:14:20</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 12:13:54</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2733f840c7d6c052b02395ced2cb1584b6b6e85ba310f4cbaba91cf7ab0e6797</t>
+          <t>7f82a1811f7869bfbec59be7b223ce268b5fb7f7514eade8aec65d378df5a299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1aee86a0efb085a75b9b3030744ffa0b</t>
+          <t>d8eed2b1b83470a8ddb56f53f0ffe461</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Laboratory Report</t>
-        </is>
+          <t>Modified After Breach</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:55</t>
+          <t>Pharmacy &amp; Prescription</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>4.7317</v>
+      </c>
+      <c r="T6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1154,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>lab_test_results_2026.csv</t>
+          <t>ehr_patient_records.csv</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>healthcare_data\lab reports\lab_test_results_2026.csv</t>
+          <t>healthcare_data\EHR\ehr_patient_records.csv</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1107,7 +1168,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.91</v>
+        <v>2.29</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1121,7 +1182,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-04-07 12:14:22</t>
+          <t>2026-04-07 12:13:54</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1131,17 +1192,17 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>ef9f2d5b367cbf71c1ddaf1ebd7af7973271ed0fda77eb0a56b149df755f0aaa</t>
+          <t>8aead1e5ff7f49a39aaac45d7ab3075ac1c5aec63998d654e88c3b95c95efb74</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>cd35e3d18d28c56919fabdb451d23a0a</t>
+          <t>3af5ca6cb0272db6e103b237a5dc1fe6</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1151,17 +1212,26 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>Laboratory Report</t>
-        </is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:55</t>
+          <t>Electronic Health Record</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>5.1397</v>
+      </c>
+      <c r="T7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1183,21 +1253,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>pharmacy_drug_inventory.txt</t>
+          <t>pharmacy_prescriptions_2026.csv</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>healthcare_data\Pharmacy\pharmacy_drug_inventory.txt</t>
+          <t>healthcare_data\Pharmacy\pharmacy_prescriptions_2026.csv</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>.txt</t>
+          <t>.csv</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.42</v>
+        <v>3.23</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1211,27 +1281,27 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:51</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:35</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7f82a1811f7869bfbec59be7b223ce268b5fb7f7514eade8aec65d378df5a299</t>
+          <t>6f91fe9b1a1ccfd7cadc6db1750cbec2829c65d347b98a97b1d5f65e6593c1dd</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>d8eed2b1b83470a8ddb56f53f0ffe461</t>
+          <t>8715ba0958638216b7051221455fafe5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1239,19 +1309,28 @@
           <t>Modified After Breach</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Pharmacy &amp; Prescription</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10 15:03:55</t>
+      <c r="S8" s="2" t="n">
+        <v>5.1344</v>
+      </c>
+      <c r="T8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1273,21 +1352,21 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>pharmacy_prescriptions_2026.csv</t>
+          <t>lab_report_P003_cardiac.txt</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>healthcare_data\Pharmacy\pharmacy_prescriptions_2026.csv</t>
+          <t>healthcare_data\lab reports\lab_report_P003_cardiac.txt</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>.csv</t>
+          <t>.txt</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.23</v>
+        <v>2.1</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -1301,47 +1380,56 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:51</t>
+          <t>2026-04-07 12:13:54</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:35</t>
+          <t>2026-04-07 12:13:54</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>6f91fe9b1a1ccfd7cadc6db1750cbec2829c65d347b98a97b1d5f65e6593c1dd</t>
+          <t>2733f840c7d6c052b02395ced2cb1584b6b6e85ba310f4cbaba91cf7ab0e6797</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>8715ba0958638216b7051221455fafe5</t>
+          <t>1aee86a0efb085a75b9b3030744ffa0b</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>Modified After Breach</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>Pharmacy &amp; Prescription</t>
-        </is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:55</t>
+          <t>Laboratory Report</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>4.8812</v>
+      </c>
+      <c r="T9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1479,17 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:56</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:35</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1419,19 +1507,28 @@
           <t>Modified After Breach</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Structured Healthcare Dataset</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10 15:03:55</t>
+      <c r="S10" s="2" t="n">
+        <v>5.1705</v>
+      </c>
+      <c r="T10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1481,17 +1578,17 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:56</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 11:19:35</t>
+          <t>2026-04-10 11:19:34</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10 15:03:32</t>
+          <t>2026-04-21 20:54:08</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1509,19 +1606,28 @@
           <t>Modified After Breach</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Medical Report</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-10 15:03:55</t>
+      <c r="S11" s="4" t="n">
+        <v>4.835</v>
+      </c>
+      <c r="T11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21 20:54:24</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1544,49 +1650,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>FORENSIC INVESTIGATION SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Total Files Scanned</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="9" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Critical Risk Files</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>High Risk Files</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Medium Risk Files</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Low Risk Files</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Anomalies Detected</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Timestomping Flags</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
